--- a/NaCl_Testing/Data/Data Sheet.xlsx
+++ b/NaCl_Testing/Data/Data Sheet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rauna\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rauna\Downloads\Paper_Sensor\NaCl_Testing\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C459701-4A2B-44CA-9E4A-B064BFBE6C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC7ACB5-1D09-4000-9900-5482E1C58AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="0" windowWidth="15810" windowHeight="15480" xr2:uid="{39D5A8A7-DD7E-420F-BBEA-66CBC6AA669C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{39D5A8A7-DD7E-420F-BBEA-66CBC6AA669C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="69">
   <si>
     <t>NaCl concentrailon data on COPPER</t>
   </si>
@@ -194,6 +194,99 @@
   </si>
   <si>
     <t>C_Data12_11</t>
+  </si>
+  <si>
+    <t>Copper_Data</t>
+  </si>
+  <si>
+    <t>Graphite_Data</t>
+  </si>
+  <si>
+    <t>NaCl Concentration Data on Graphite INK</t>
+  </si>
+  <si>
+    <t>Graphite_INK_Data</t>
+  </si>
+  <si>
+    <t>GI_Data01_00</t>
+  </si>
+  <si>
+    <t>GI_Data02_01</t>
+  </si>
+  <si>
+    <t>GI_Data03_02</t>
+  </si>
+  <si>
+    <t>GI_Data04_03</t>
+  </si>
+  <si>
+    <t>GI_Data05_04</t>
+  </si>
+  <si>
+    <t>GI_Data07_06</t>
+  </si>
+  <si>
+    <t>GI_Data06_05</t>
+  </si>
+  <si>
+    <t>GI_Data08_07</t>
+  </si>
+  <si>
+    <t>GI_Data09_08</t>
+  </si>
+  <si>
+    <t>GI_Data10_09</t>
+  </si>
+  <si>
+    <t>GI_Data11_10</t>
+  </si>
+  <si>
+    <t>GI_Data12_11</t>
+  </si>
+  <si>
+    <t>Solid_Graphite_Data</t>
+  </si>
+  <si>
+    <t>SG_Data01_00</t>
+  </si>
+  <si>
+    <t>SG_Data02_01</t>
+  </si>
+  <si>
+    <t>SG_Data03_02</t>
+  </si>
+  <si>
+    <t>SG_Data04_03</t>
+  </si>
+  <si>
+    <t>SG_Data05_04</t>
+  </si>
+  <si>
+    <t>SG_Data06_05</t>
+  </si>
+  <si>
+    <t>SG_Data07_06</t>
+  </si>
+  <si>
+    <t>SG_Data08_07</t>
+  </si>
+  <si>
+    <t>SG_Data09_08</t>
+  </si>
+  <si>
+    <t>SG_Data10_09</t>
+  </si>
+  <si>
+    <t>SG_Data11_10</t>
+  </si>
+  <si>
+    <t>SG_Data12_11</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Resistance R0 (K)</t>
   </si>
 </sst>
 </file>
@@ -572,7 +665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5327C599-1361-43BB-9F82-88FAD2BF56E9}">
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:AI19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="13" customWidth="1"/>
@@ -584,175 +677,245 @@
     <col min="14" max="14" width="22.7109375" customWidth="1"/>
     <col min="15" max="15" width="21" customWidth="1"/>
     <col min="16" max="16" width="19.42578125" customWidth="1"/>
+    <col min="20" max="20" width="12.85546875" customWidth="1"/>
+    <col min="21" max="21" width="13.140625" customWidth="1"/>
+    <col min="22" max="22" width="11.85546875" customWidth="1"/>
+    <col min="23" max="23" width="12.7109375" customWidth="1"/>
+    <col min="24" max="24" width="18.85546875" customWidth="1"/>
+    <col min="25" max="25" width="20.140625" customWidth="1"/>
+    <col min="26" max="26" width="16.7109375" customWidth="1"/>
+    <col min="30" max="30" width="11.85546875" customWidth="1"/>
+    <col min="31" max="31" width="11.42578125" customWidth="1"/>
+    <col min="32" max="32" width="10.7109375" customWidth="1"/>
+    <col min="33" max="33" width="13" customWidth="1"/>
+    <col min="34" max="34" width="18.42578125" customWidth="1"/>
+    <col min="35" max="35" width="18.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="S1" s="1" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3" t="s">
         <v>4</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D3" t="s">
         <v>5</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E3" t="s">
         <v>14</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F3" t="s">
         <v>2</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I3" t="s">
         <v>1</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J3" t="s">
         <v>8</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K3" t="s">
         <v>4</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L3" t="s">
         <v>9</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M3" t="s">
         <v>14</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N3" t="s">
         <v>11</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O3" t="s">
         <v>12</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S3" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V3" t="s">
+        <v>9</v>
+      </c>
+      <c r="W3" t="s">
+        <v>14</v>
+      </c>
+      <c r="X3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A4">
         <v>1</v>
       </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
         <v>6</v>
       </c>
-      <c r="I3">
+      <c r="I4">
         <v>1</v>
       </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
         <v>6</v>
-      </c>
-      <c r="O3">
-        <v>7.2</v>
-      </c>
-      <c r="P3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>20</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>22.2</v>
-      </c>
-      <c r="E4">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>20</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>22.2</v>
-      </c>
-      <c r="M4">
-        <v>10</v>
-      </c>
-      <c r="N4">
-        <v>6.1</v>
       </c>
       <c r="O4">
         <v>7.2</v>
       </c>
       <c r="P4" t="s">
-        <v>13</v>
+        <v>6</v>
+      </c>
+      <c r="S4">
+        <v>1</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC4">
+        <v>1</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>2.6</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5">
         <v>20</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="E5">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J5">
         <v>20</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5">
         <v>22.2</v>
@@ -761,156 +924,300 @@
         <v>10</v>
       </c>
       <c r="N5">
+        <v>6.1</v>
+      </c>
+      <c r="O5">
+        <v>7.2</v>
+      </c>
+      <c r="P5" t="s">
+        <v>13</v>
+      </c>
+      <c r="S5">
+        <v>2</v>
+      </c>
+      <c r="T5">
+        <v>20</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>18.2</v>
+      </c>
+      <c r="W5">
+        <v>10</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC5">
+        <v>2</v>
+      </c>
+      <c r="AD5">
+        <v>20</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>18.2</v>
+      </c>
+      <c r="AG5">
+        <v>10</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>20</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>22.3</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <v>20</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>22.2</v>
+      </c>
+      <c r="M6">
+        <v>10</v>
+      </c>
+      <c r="N6">
         <v>6.7</v>
       </c>
-      <c r="O5">
+      <c r="O6">
         <v>11.2</v>
       </c>
-      <c r="P5" t="s">
+      <c r="P6" t="s">
         <v>15</v>
       </c>
+      <c r="S6">
+        <v>3</v>
+      </c>
+      <c r="T6">
+        <v>20</v>
+      </c>
+      <c r="U6">
+        <v>1</v>
+      </c>
+      <c r="V6">
+        <v>18.2</v>
+      </c>
+      <c r="W6">
+        <v>10</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC6">
+        <v>3</v>
+      </c>
+      <c r="AD6">
+        <v>20</v>
+      </c>
+      <c r="AE6">
+        <v>1</v>
+      </c>
+      <c r="AF6">
+        <v>18.2</v>
+      </c>
+      <c r="AG6">
+        <v>10</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>56</v>
+      </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A7">
         <v>4</v>
       </c>
-      <c r="B6">
-        <v>20</v>
-      </c>
-      <c r="C6">
+      <c r="B7">
+        <v>20</v>
+      </c>
+      <c r="C7">
         <v>2</v>
       </c>
-      <c r="D6">
+      <c r="D7">
         <v>22.2</v>
       </c>
-      <c r="E6">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="E7">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
         <v>28</v>
       </c>
-      <c r="I6">
+      <c r="I7">
         <v>4</v>
       </c>
-      <c r="J6">
-        <v>20</v>
-      </c>
-      <c r="K6">
+      <c r="J7">
+        <v>20</v>
+      </c>
+      <c r="K7">
         <v>2</v>
       </c>
-      <c r="L6">
+      <c r="L7">
         <v>22.3</v>
       </c>
-      <c r="M6">
-        <v>10</v>
-      </c>
-      <c r="N6">
+      <c r="M7">
+        <v>10</v>
+      </c>
+      <c r="N7">
         <v>4.0999999999999996</v>
       </c>
-      <c r="O6">
+      <c r="O7">
         <v>8.1999999999999993</v>
       </c>
-      <c r="P6" t="s">
+      <c r="P7" t="s">
         <v>16</v>
       </c>
+      <c r="S7">
+        <v>4</v>
+      </c>
+      <c r="T7">
+        <v>20</v>
+      </c>
+      <c r="U7">
+        <v>2</v>
+      </c>
+      <c r="V7">
+        <v>18.2</v>
+      </c>
+      <c r="W7">
+        <v>10</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC7">
+        <v>4</v>
+      </c>
+      <c r="AD7">
+        <v>20</v>
+      </c>
+      <c r="AE7">
+        <v>2</v>
+      </c>
+      <c r="AF7">
+        <v>18.2</v>
+      </c>
+      <c r="AG7">
+        <v>10</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>57</v>
+      </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A8">
         <v>5</v>
       </c>
-      <c r="B7">
-        <v>20</v>
-      </c>
-      <c r="C7">
+      <c r="B8">
+        <v>20</v>
+      </c>
+      <c r="C8">
         <v>3</v>
       </c>
-      <c r="D7">
+      <c r="D8">
         <v>22.3</v>
       </c>
-      <c r="E7">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="E8">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
         <v>29</v>
       </c>
-      <c r="I7">
+      <c r="I8">
         <v>5</v>
       </c>
-      <c r="J7">
-        <v>20</v>
-      </c>
-      <c r="K7">
+      <c r="J8">
+        <v>20</v>
+      </c>
+      <c r="K8">
         <v>3</v>
       </c>
-      <c r="L7">
+      <c r="L8">
         <v>22.2</v>
       </c>
-      <c r="M7">
-        <v>10</v>
-      </c>
-      <c r="N7">
+      <c r="M8">
+        <v>10</v>
+      </c>
+      <c r="N8">
         <v>8.1</v>
       </c>
-      <c r="O7">
+      <c r="O8">
         <v>6.9</v>
       </c>
-      <c r="P7" t="s">
+      <c r="P8" t="s">
         <v>17</v>
       </c>
+      <c r="S8">
+        <v>5</v>
+      </c>
+      <c r="T8">
+        <v>20</v>
+      </c>
+      <c r="U8">
+        <v>3</v>
+      </c>
+      <c r="V8">
+        <v>18.2</v>
+      </c>
+      <c r="W8">
+        <v>10</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC8">
+        <v>5</v>
+      </c>
+      <c r="AD8">
+        <v>20</v>
+      </c>
+      <c r="AE8">
+        <v>3</v>
+      </c>
+      <c r="AF8">
+        <v>18.2</v>
+      </c>
+      <c r="AG8">
+        <v>10</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>58</v>
+      </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A9">
         <v>6</v>
       </c>
-      <c r="B8">
-        <v>20</v>
-      </c>
-      <c r="C8">
+      <c r="B9">
+        <v>20</v>
+      </c>
+      <c r="C9">
         <v>4</v>
-      </c>
-      <c r="D8">
-        <v>22.2</v>
-      </c>
-      <c r="E8">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I8">
-        <v>6</v>
-      </c>
-      <c r="J8">
-        <v>20</v>
-      </c>
-      <c r="K8">
-        <v>4</v>
-      </c>
-      <c r="L8">
-        <v>22.3</v>
-      </c>
-      <c r="M8">
-        <v>10</v>
-      </c>
-      <c r="N8">
-        <v>7.6</v>
-      </c>
-      <c r="O8">
-        <v>7.9</v>
-      </c>
-      <c r="P8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>20</v>
-      </c>
-      <c r="C9">
-        <v>5</v>
       </c>
       <c r="D9">
         <v>22.2</v>
@@ -919,16 +1226,16 @@
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J9">
         <v>20</v>
       </c>
       <c r="K9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L9">
         <v>22.3</v>
@@ -937,24 +1244,60 @@
         <v>10</v>
       </c>
       <c r="N9">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="O9">
-        <v>7.1</v>
+        <v>7.9</v>
       </c>
       <c r="P9" t="s">
-        <v>19</v>
+        <v>18</v>
+      </c>
+      <c r="S9">
+        <v>6</v>
+      </c>
+      <c r="T9">
+        <v>20</v>
+      </c>
+      <c r="U9">
+        <v>4</v>
+      </c>
+      <c r="V9">
+        <v>18.2</v>
+      </c>
+      <c r="W9">
+        <v>10</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC9">
+        <v>6</v>
+      </c>
+      <c r="AD9">
+        <v>20</v>
+      </c>
+      <c r="AE9">
+        <v>4</v>
+      </c>
+      <c r="AF9">
+        <v>18.2</v>
+      </c>
+      <c r="AG9">
+        <v>10</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10">
         <v>20</v>
       </c>
       <c r="C10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10">
         <v>22.2</v>
@@ -963,16 +1306,16 @@
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J10">
         <v>20</v>
       </c>
       <c r="K10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <v>22.3</v>
@@ -981,24 +1324,60 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="O10">
-        <v>8.6</v>
+        <v>7.1</v>
       </c>
       <c r="P10" t="s">
-        <v>20</v>
+        <v>19</v>
+      </c>
+      <c r="S10">
+        <v>7</v>
+      </c>
+      <c r="T10">
+        <v>20</v>
+      </c>
+      <c r="U10">
+        <v>5</v>
+      </c>
+      <c r="V10">
+        <v>18.2</v>
+      </c>
+      <c r="W10">
+        <v>10</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC10">
+        <v>7</v>
+      </c>
+      <c r="AD10">
+        <v>20</v>
+      </c>
+      <c r="AE10">
+        <v>5</v>
+      </c>
+      <c r="AF10">
+        <v>18.2</v>
+      </c>
+      <c r="AG10">
+        <v>10</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11">
         <v>20</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D11">
         <v>22.2</v>
@@ -1007,60 +1386,96 @@
         <v>10</v>
       </c>
       <c r="F11" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11">
+        <v>8</v>
+      </c>
+      <c r="J11">
+        <v>20</v>
+      </c>
+      <c r="K11">
+        <v>6</v>
+      </c>
+      <c r="L11">
+        <v>22.3</v>
+      </c>
+      <c r="M11">
+        <v>10</v>
+      </c>
+      <c r="N11">
+        <v>5.8</v>
+      </c>
+      <c r="O11">
+        <v>8.6</v>
+      </c>
+      <c r="P11" t="s">
+        <v>20</v>
+      </c>
+      <c r="S11">
+        <v>8</v>
+      </c>
+      <c r="T11">
+        <v>20</v>
+      </c>
+      <c r="U11">
+        <v>6</v>
+      </c>
+      <c r="V11">
+        <v>18.2</v>
+      </c>
+      <c r="W11">
+        <v>10</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC11">
+        <v>8</v>
+      </c>
+      <c r="AD11">
+        <v>20</v>
+      </c>
+      <c r="AE11">
+        <v>6</v>
+      </c>
+      <c r="AF11">
+        <v>18.2</v>
+      </c>
+      <c r="AG11">
+        <v>10</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12">
+        <v>20</v>
+      </c>
+      <c r="C12">
+        <v>7</v>
+      </c>
+      <c r="D12">
+        <v>22.2</v>
+      </c>
+      <c r="E12">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
         <v>33</v>
       </c>
-      <c r="I11">
+      <c r="I12">
         <v>9</v>
       </c>
-      <c r="J11">
-        <v>20</v>
-      </c>
-      <c r="K11">
+      <c r="J12">
+        <v>20</v>
+      </c>
+      <c r="K12">
         <v>7</v>
-      </c>
-      <c r="L11">
-        <v>22.2</v>
-      </c>
-      <c r="M11">
-        <v>10</v>
-      </c>
-      <c r="N11">
-        <v>12.2</v>
-      </c>
-      <c r="O11">
-        <v>6.4</v>
-      </c>
-      <c r="P11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>10</v>
-      </c>
-      <c r="B12">
-        <v>20</v>
-      </c>
-      <c r="C12">
-        <v>8</v>
-      </c>
-      <c r="D12">
-        <v>22.1</v>
-      </c>
-      <c r="E12">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>34</v>
-      </c>
-      <c r="I12">
-        <v>10</v>
-      </c>
-      <c r="J12">
-        <v>20</v>
-      </c>
-      <c r="K12">
-        <v>8</v>
       </c>
       <c r="L12">
         <v>22.2</v>
@@ -1069,86 +1484,158 @@
         <v>10</v>
       </c>
       <c r="N12">
+        <v>12.2</v>
+      </c>
+      <c r="O12">
+        <v>6.4</v>
+      </c>
+      <c r="P12" t="s">
+        <v>21</v>
+      </c>
+      <c r="S12">
+        <v>9</v>
+      </c>
+      <c r="T12">
+        <v>20</v>
+      </c>
+      <c r="U12">
+        <v>7</v>
+      </c>
+      <c r="V12">
+        <v>18.2</v>
+      </c>
+      <c r="W12">
+        <v>10</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC12">
+        <v>9</v>
+      </c>
+      <c r="AD12">
+        <v>20</v>
+      </c>
+      <c r="AE12">
+        <v>7</v>
+      </c>
+      <c r="AF12">
+        <v>18.2</v>
+      </c>
+      <c r="AG12">
+        <v>10</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13">
+        <v>20</v>
+      </c>
+      <c r="C13">
+        <v>8</v>
+      </c>
+      <c r="D13">
+        <v>22.1</v>
+      </c>
+      <c r="E13">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>34</v>
+      </c>
+      <c r="I13">
+        <v>10</v>
+      </c>
+      <c r="J13">
+        <v>20</v>
+      </c>
+      <c r="K13">
+        <v>8</v>
+      </c>
+      <c r="L13">
+        <v>22.2</v>
+      </c>
+      <c r="M13">
+        <v>10</v>
+      </c>
+      <c r="N13">
         <v>6.5</v>
       </c>
-      <c r="O12">
+      <c r="O13">
         <v>11.2</v>
       </c>
-      <c r="P12" t="s">
+      <c r="P13" t="s">
         <v>22</v>
       </c>
+      <c r="S13">
+        <v>10</v>
+      </c>
+      <c r="T13">
+        <v>20</v>
+      </c>
+      <c r="U13">
+        <v>8</v>
+      </c>
+      <c r="V13">
+        <v>18.2</v>
+      </c>
+      <c r="W13">
+        <v>10</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC13">
+        <v>10</v>
+      </c>
+      <c r="AD13">
+        <v>20</v>
+      </c>
+      <c r="AE13">
+        <v>8</v>
+      </c>
+      <c r="AF13">
+        <v>18.2</v>
+      </c>
+      <c r="AG13">
+        <v>10</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>63</v>
+      </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A14">
         <v>11</v>
       </c>
-      <c r="B13">
-        <v>20</v>
-      </c>
-      <c r="C13">
+      <c r="B14">
+        <v>20</v>
+      </c>
+      <c r="C14">
         <v>9</v>
       </c>
-      <c r="D13">
+      <c r="D14">
         <v>22.2</v>
       </c>
-      <c r="E13">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="E14">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
         <v>35</v>
       </c>
-      <c r="I13">
+      <c r="I14">
         <v>11</v>
       </c>
-      <c r="J13">
-        <v>20</v>
-      </c>
-      <c r="K13">
+      <c r="J14">
+        <v>20</v>
+      </c>
+      <c r="K14">
         <v>9</v>
-      </c>
-      <c r="L13">
-        <v>22.3</v>
-      </c>
-      <c r="M13">
-        <v>10</v>
-      </c>
-      <c r="N13">
-        <v>5.9</v>
-      </c>
-      <c r="O13">
-        <v>12.1</v>
-      </c>
-      <c r="P13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>12</v>
-      </c>
-      <c r="B14">
-        <v>20</v>
-      </c>
-      <c r="C14">
-        <v>10</v>
-      </c>
-      <c r="D14">
-        <v>22.3</v>
-      </c>
-      <c r="E14">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>36</v>
-      </c>
-      <c r="I14">
-        <v>12</v>
-      </c>
-      <c r="J14">
-        <v>20</v>
-      </c>
-      <c r="K14">
-        <v>10</v>
       </c>
       <c r="L14">
         <v>22.3</v>
@@ -1157,24 +1644,60 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>42.5</v>
+        <v>5.9</v>
       </c>
       <c r="O14">
-        <v>22.3</v>
+        <v>12.1</v>
       </c>
       <c r="P14" t="s">
-        <v>24</v>
+        <v>23</v>
+      </c>
+      <c r="S14">
+        <v>11</v>
+      </c>
+      <c r="T14">
+        <v>20</v>
+      </c>
+      <c r="U14">
+        <v>9</v>
+      </c>
+      <c r="V14">
+        <v>18.2</v>
+      </c>
+      <c r="W14">
+        <v>10</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>51</v>
+      </c>
+      <c r="AC14">
+        <v>11</v>
+      </c>
+      <c r="AD14">
+        <v>20</v>
+      </c>
+      <c r="AE14">
+        <v>9</v>
+      </c>
+      <c r="AF14">
+        <v>18.2</v>
+      </c>
+      <c r="AG14">
+        <v>10</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15">
         <v>20</v>
       </c>
       <c r="C15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D15">
         <v>22.3</v>
@@ -1183,16 +1706,16 @@
         <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J15">
         <v>20</v>
       </c>
       <c r="K15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L15">
         <v>22.3</v>
@@ -1201,13 +1724,134 @@
         <v>10</v>
       </c>
       <c r="N15">
+        <v>42.5</v>
+      </c>
+      <c r="O15">
+        <v>22.3</v>
+      </c>
+      <c r="P15" t="s">
+        <v>24</v>
+      </c>
+      <c r="S15">
+        <v>12</v>
+      </c>
+      <c r="T15">
+        <v>20</v>
+      </c>
+      <c r="U15">
+        <v>10</v>
+      </c>
+      <c r="V15">
+        <v>18.2</v>
+      </c>
+      <c r="W15">
+        <v>10</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC15">
+        <v>12</v>
+      </c>
+      <c r="AD15">
+        <v>20</v>
+      </c>
+      <c r="AE15">
+        <v>10</v>
+      </c>
+      <c r="AF15">
+        <v>18.2</v>
+      </c>
+      <c r="AG15">
+        <v>10</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>13</v>
+      </c>
+      <c r="B16">
+        <v>20</v>
+      </c>
+      <c r="C16">
+        <v>11</v>
+      </c>
+      <c r="D16">
+        <v>22.3</v>
+      </c>
+      <c r="E16">
+        <v>10</v>
+      </c>
+      <c r="F16" t="s">
+        <v>37</v>
+      </c>
+      <c r="I16">
+        <v>13</v>
+      </c>
+      <c r="J16">
+        <v>20</v>
+      </c>
+      <c r="K16">
+        <v>11</v>
+      </c>
+      <c r="L16">
+        <v>22.3</v>
+      </c>
+      <c r="M16">
+        <v>10</v>
+      </c>
+      <c r="N16">
         <v>13.6</v>
       </c>
-      <c r="O15">
+      <c r="O16">
         <v>17.899999999999999</v>
       </c>
-      <c r="P15" t="s">
+      <c r="P16" t="s">
         <v>25</v>
+      </c>
+      <c r="S16">
+        <v>13</v>
+      </c>
+      <c r="T16">
+        <v>20</v>
+      </c>
+      <c r="U16">
+        <v>11</v>
+      </c>
+      <c r="V16">
+        <v>18.2</v>
+      </c>
+      <c r="W16">
+        <v>10</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC16">
+        <v>13</v>
+      </c>
+      <c r="AD16">
+        <v>20</v>
+      </c>
+      <c r="AE16">
+        <v>11</v>
+      </c>
+      <c r="AF16">
+        <v>18.2</v>
+      </c>
+      <c r="AG16">
+        <v>10</v>
+      </c>
+      <c r="AI16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI19" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/NaCl_Testing/Data/Data Sheet.xlsx
+++ b/NaCl_Testing/Data/Data Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rauna\Downloads\Paper_Sensor\NaCl_Testing\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC7ACB5-1D09-4000-9900-5482E1C58AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7BE8D5-769F-4754-84D9-CAA10E5D5E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{39D5A8A7-DD7E-420F-BBEA-66CBC6AA669C}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="93">
   <si>
     <t>NaCl concentrailon data on COPPER</t>
   </si>
@@ -287,6 +287,78 @@
   </si>
   <si>
     <t>Resistance R0 (K)</t>
+  </si>
+  <si>
+    <t>C_Data13_00</t>
+  </si>
+  <si>
+    <t>C_Data14_01</t>
+  </si>
+  <si>
+    <t>C_Data15_02</t>
+  </si>
+  <si>
+    <t>C_Data16_03</t>
+  </si>
+  <si>
+    <t>C_Data17_04</t>
+  </si>
+  <si>
+    <t>C_Data18_05</t>
+  </si>
+  <si>
+    <t>C_Data19_06</t>
+  </si>
+  <si>
+    <t>C_Data20_07</t>
+  </si>
+  <si>
+    <t>C_Data21_08</t>
+  </si>
+  <si>
+    <t>C_Data22_09</t>
+  </si>
+  <si>
+    <t>C_Data23_10</t>
+  </si>
+  <si>
+    <t>C_Data23_11</t>
+  </si>
+  <si>
+    <t>G_Data13_00</t>
+  </si>
+  <si>
+    <t>G_Data14_01</t>
+  </si>
+  <si>
+    <t>G_Data15_02</t>
+  </si>
+  <si>
+    <t>G_Data16_03</t>
+  </si>
+  <si>
+    <t>G_Data17_04</t>
+  </si>
+  <si>
+    <t>G_Data18_05</t>
+  </si>
+  <si>
+    <t>G_Data19_06</t>
+  </si>
+  <si>
+    <t>G_Data20_07</t>
+  </si>
+  <si>
+    <t>G_Data21_08</t>
+  </si>
+  <si>
+    <t>G_Data22_09</t>
+  </si>
+  <si>
+    <t>G_Data23_10</t>
+  </si>
+  <si>
+    <t>G_Data24_11</t>
   </si>
 </sst>
 </file>
@@ -665,7 +737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5327C599-1361-43BB-9F82-88FAD2BF56E9}">
-  <dimension ref="A1:AI19"/>
+  <dimension ref="A1:AI28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="13" customWidth="1"/>
@@ -864,6 +936,12 @@
       <c r="W4">
         <v>0</v>
       </c>
+      <c r="X4">
+        <v>0.82</v>
+      </c>
+      <c r="Y4">
+        <v>0.33</v>
+      </c>
       <c r="Z4" t="s">
         <v>6</v>
       </c>
@@ -947,6 +1025,12 @@
       <c r="W5">
         <v>10</v>
       </c>
+      <c r="X5">
+        <v>0.82</v>
+      </c>
+      <c r="Y5">
+        <v>0.33</v>
+      </c>
       <c r="Z5" t="s">
         <v>42</v>
       </c>
@@ -964,6 +1048,9 @@
       </c>
       <c r="AG5">
         <v>10</v>
+      </c>
+      <c r="AH5">
+        <v>2.6</v>
       </c>
       <c r="AI5" t="s">
         <v>55</v>
@@ -1027,6 +1114,12 @@
       <c r="W6">
         <v>10</v>
       </c>
+      <c r="X6">
+        <v>0.6</v>
+      </c>
+      <c r="Y6">
+        <v>1.9</v>
+      </c>
       <c r="Z6" t="s">
         <v>43</v>
       </c>
@@ -1044,6 +1137,9 @@
       </c>
       <c r="AG6">
         <v>10</v>
+      </c>
+      <c r="AH6">
+        <v>5.6</v>
       </c>
       <c r="AI6" t="s">
         <v>56</v>
@@ -1107,6 +1203,12 @@
       <c r="W7">
         <v>10</v>
       </c>
+      <c r="X7">
+        <v>1.3</v>
+      </c>
+      <c r="Y7">
+        <v>1.5</v>
+      </c>
       <c r="Z7" t="s">
         <v>44</v>
       </c>
@@ -1124,6 +1226,9 @@
       </c>
       <c r="AG7">
         <v>10</v>
+      </c>
+      <c r="AH7">
+        <v>14.8</v>
       </c>
       <c r="AI7" t="s">
         <v>57</v>
@@ -1187,6 +1292,12 @@
       <c r="W8">
         <v>10</v>
       </c>
+      <c r="X8">
+        <v>0.5</v>
+      </c>
+      <c r="Y8">
+        <v>0.2</v>
+      </c>
       <c r="Z8" t="s">
         <v>45</v>
       </c>
@@ -1204,6 +1315,9 @@
       </c>
       <c r="AG8">
         <v>10</v>
+      </c>
+      <c r="AH8">
+        <v>5.2</v>
       </c>
       <c r="AI8" t="s">
         <v>58</v>
@@ -1267,6 +1381,12 @@
       <c r="W9">
         <v>10</v>
       </c>
+      <c r="X9">
+        <v>0.7</v>
+      </c>
+      <c r="Y9">
+        <v>0.4</v>
+      </c>
       <c r="Z9" t="s">
         <v>46</v>
       </c>
@@ -1284,6 +1404,9 @@
       </c>
       <c r="AG9">
         <v>10</v>
+      </c>
+      <c r="AH9">
+        <v>11.4</v>
       </c>
       <c r="AI9" t="s">
         <v>59</v>
@@ -1347,6 +1470,12 @@
       <c r="W10">
         <v>10</v>
       </c>
+      <c r="X10">
+        <v>0.53</v>
+      </c>
+      <c r="Y10">
+        <v>0.75</v>
+      </c>
       <c r="Z10" t="s">
         <v>48</v>
       </c>
@@ -1364,6 +1493,9 @@
       </c>
       <c r="AG10">
         <v>10</v>
+      </c>
+      <c r="AH10">
+        <v>11.7</v>
       </c>
       <c r="AI10" t="s">
         <v>60</v>
@@ -1427,6 +1559,12 @@
       <c r="W11">
         <v>10</v>
       </c>
+      <c r="X11">
+        <v>1.2</v>
+      </c>
+      <c r="Y11">
+        <v>0.8</v>
+      </c>
       <c r="Z11" t="s">
         <v>47</v>
       </c>
@@ -1444,6 +1582,9 @@
       </c>
       <c r="AG11">
         <v>10</v>
+      </c>
+      <c r="AH11">
+        <v>3.7</v>
       </c>
       <c r="AI11" t="s">
         <v>61</v>
@@ -1507,6 +1648,9 @@
       <c r="W12">
         <v>10</v>
       </c>
+      <c r="X12">
+        <v>1.6</v>
+      </c>
       <c r="Z12" t="s">
         <v>49</v>
       </c>
@@ -1525,6 +1669,9 @@
       <c r="AG12">
         <v>10</v>
       </c>
+      <c r="AH12">
+        <v>7.1</v>
+      </c>
       <c r="AI12" t="s">
         <v>62</v>
       </c>
@@ -1587,6 +1734,12 @@
       <c r="W13">
         <v>10</v>
       </c>
+      <c r="X13">
+        <v>0.4</v>
+      </c>
+      <c r="Y13">
+        <v>0.72</v>
+      </c>
       <c r="Z13" t="s">
         <v>50</v>
       </c>
@@ -1604,6 +1757,9 @@
       </c>
       <c r="AG13">
         <v>10</v>
+      </c>
+      <c r="AH13">
+        <v>12.03</v>
       </c>
       <c r="AI13" t="s">
         <v>63</v>
@@ -1667,6 +1823,12 @@
       <c r="W14">
         <v>10</v>
       </c>
+      <c r="X14">
+        <v>0.33</v>
+      </c>
+      <c r="Y14">
+        <v>0.51</v>
+      </c>
       <c r="Z14" t="s">
         <v>51</v>
       </c>
@@ -1684,6 +1846,9 @@
       </c>
       <c r="AG14">
         <v>10</v>
+      </c>
+      <c r="AH14">
+        <v>13.2</v>
       </c>
       <c r="AI14" t="s">
         <v>64</v>
@@ -1747,6 +1912,12 @@
       <c r="W15">
         <v>10</v>
       </c>
+      <c r="X15">
+        <v>0.67</v>
+      </c>
+      <c r="Y15">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="Z15" t="s">
         <v>52</v>
       </c>
@@ -1764,6 +1935,9 @@
       </c>
       <c r="AG15">
         <v>10</v>
+      </c>
+      <c r="AH15">
+        <v>13.5</v>
       </c>
       <c r="AI15" t="s">
         <v>65</v>
@@ -1827,6 +2001,12 @@
       <c r="W16">
         <v>10</v>
       </c>
+      <c r="X16">
+        <v>1.7</v>
+      </c>
+      <c r="Y16">
+        <v>1.2</v>
+      </c>
       <c r="Z16" t="s">
         <v>53</v>
       </c>
@@ -1845,13 +2025,542 @@
       <c r="AG16">
         <v>10</v>
       </c>
+      <c r="AH16">
+        <v>9.4</v>
+      </c>
       <c r="AI16" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="35:35" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17">
+        <v>20</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>18.2</v>
+      </c>
+      <c r="E17">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
+        <v>69</v>
+      </c>
+      <c r="I17">
+        <v>14</v>
+      </c>
+      <c r="J17">
+        <v>20</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>18.2</v>
+      </c>
+      <c r="M17">
+        <v>10</v>
+      </c>
+      <c r="N17">
+        <v>11.1</v>
+      </c>
+      <c r="O17">
+        <v>9.2100000000000009</v>
+      </c>
+      <c r="P17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>15</v>
+      </c>
+      <c r="B18">
+        <v>20</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>18.2</v>
+      </c>
+      <c r="E18">
+        <v>10</v>
+      </c>
+      <c r="F18" t="s">
+        <v>70</v>
+      </c>
+      <c r="I18">
+        <v>15</v>
+      </c>
+      <c r="J18">
+        <v>20</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>18.2</v>
+      </c>
+      <c r="M18">
+        <v>10</v>
+      </c>
+      <c r="N18">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="O18">
+        <v>16.09</v>
+      </c>
+      <c r="P18" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="B19">
+        <v>20</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <v>18.2</v>
+      </c>
+      <c r="E19">
+        <v>10</v>
+      </c>
+      <c r="F19" t="s">
+        <v>71</v>
+      </c>
+      <c r="I19">
+        <v>16</v>
+      </c>
+      <c r="J19">
+        <v>20</v>
+      </c>
+      <c r="K19">
+        <v>2</v>
+      </c>
+      <c r="L19">
+        <v>18.2</v>
+      </c>
+      <c r="M19">
+        <v>10</v>
+      </c>
+      <c r="N19">
+        <v>19.7</v>
+      </c>
+      <c r="O19">
+        <v>21.7</v>
+      </c>
+      <c r="P19" t="s">
+        <v>83</v>
+      </c>
       <c r="AI19" t="s">
         <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>17</v>
+      </c>
+      <c r="B20">
+        <v>20</v>
+      </c>
+      <c r="C20">
+        <v>3</v>
+      </c>
+      <c r="D20">
+        <v>18.2</v>
+      </c>
+      <c r="E20">
+        <v>10</v>
+      </c>
+      <c r="F20" t="s">
+        <v>72</v>
+      </c>
+      <c r="I20">
+        <v>17</v>
+      </c>
+      <c r="J20">
+        <v>20</v>
+      </c>
+      <c r="K20">
+        <v>3</v>
+      </c>
+      <c r="L20">
+        <v>18.2</v>
+      </c>
+      <c r="M20">
+        <v>10</v>
+      </c>
+      <c r="N20">
+        <v>15.4</v>
+      </c>
+      <c r="O20">
+        <v>21.4</v>
+      </c>
+      <c r="P20" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>18</v>
+      </c>
+      <c r="B21">
+        <v>20</v>
+      </c>
+      <c r="C21">
+        <v>4</v>
+      </c>
+      <c r="D21">
+        <v>18.2</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+      <c r="F21" t="s">
+        <v>73</v>
+      </c>
+      <c r="I21">
+        <v>18</v>
+      </c>
+      <c r="J21">
+        <v>20</v>
+      </c>
+      <c r="K21">
+        <v>4</v>
+      </c>
+      <c r="L21">
+        <v>18.2</v>
+      </c>
+      <c r="M21">
+        <v>10</v>
+      </c>
+      <c r="N21">
+        <v>16</v>
+      </c>
+      <c r="O21">
+        <v>17</v>
+      </c>
+      <c r="P21" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>19</v>
+      </c>
+      <c r="B22">
+        <v>20</v>
+      </c>
+      <c r="C22">
+        <v>5</v>
+      </c>
+      <c r="D22">
+        <v>18.2</v>
+      </c>
+      <c r="E22">
+        <v>10</v>
+      </c>
+      <c r="F22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I22">
+        <v>19</v>
+      </c>
+      <c r="J22">
+        <v>20</v>
+      </c>
+      <c r="K22">
+        <v>5</v>
+      </c>
+      <c r="L22">
+        <v>18.2</v>
+      </c>
+      <c r="M22">
+        <v>10</v>
+      </c>
+      <c r="N22">
+        <v>12.3</v>
+      </c>
+      <c r="O22">
+        <v>12.5</v>
+      </c>
+      <c r="P22" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>20</v>
+      </c>
+      <c r="B23">
+        <v>20</v>
+      </c>
+      <c r="C23">
+        <v>6</v>
+      </c>
+      <c r="D23">
+        <v>18.2</v>
+      </c>
+      <c r="E23">
+        <v>10</v>
+      </c>
+      <c r="F23" t="s">
+        <v>75</v>
+      </c>
+      <c r="I23">
+        <v>20</v>
+      </c>
+      <c r="J23">
+        <v>20</v>
+      </c>
+      <c r="K23">
+        <v>6</v>
+      </c>
+      <c r="L23">
+        <v>18.2</v>
+      </c>
+      <c r="M23">
+        <v>10</v>
+      </c>
+      <c r="N23">
+        <v>22.3</v>
+      </c>
+      <c r="O23">
+        <v>22.1</v>
+      </c>
+      <c r="P23" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="24" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>21</v>
+      </c>
+      <c r="B24">
+        <v>20</v>
+      </c>
+      <c r="C24">
+        <v>7</v>
+      </c>
+      <c r="D24">
+        <v>18.2</v>
+      </c>
+      <c r="E24">
+        <v>10</v>
+      </c>
+      <c r="F24" t="s">
+        <v>76</v>
+      </c>
+      <c r="I24">
+        <v>21</v>
+      </c>
+      <c r="J24">
+        <v>20</v>
+      </c>
+      <c r="K24">
+        <v>7</v>
+      </c>
+      <c r="L24">
+        <v>18.2</v>
+      </c>
+      <c r="M24">
+        <v>10</v>
+      </c>
+      <c r="N24">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="O24">
+        <v>16</v>
+      </c>
+      <c r="P24" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>22</v>
+      </c>
+      <c r="B25">
+        <v>20</v>
+      </c>
+      <c r="C25">
+        <v>8</v>
+      </c>
+      <c r="D25">
+        <v>18.2</v>
+      </c>
+      <c r="E25">
+        <v>10</v>
+      </c>
+      <c r="F25" t="s">
+        <v>77</v>
+      </c>
+      <c r="I25">
+        <v>22</v>
+      </c>
+      <c r="J25">
+        <v>20</v>
+      </c>
+      <c r="K25">
+        <v>8</v>
+      </c>
+      <c r="L25">
+        <v>18.2</v>
+      </c>
+      <c r="M25">
+        <v>10</v>
+      </c>
+      <c r="N25">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="O25">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="P25" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>23</v>
+      </c>
+      <c r="B26">
+        <v>20</v>
+      </c>
+      <c r="C26">
+        <v>9</v>
+      </c>
+      <c r="D26">
+        <v>18.2</v>
+      </c>
+      <c r="E26">
+        <v>10</v>
+      </c>
+      <c r="F26" t="s">
+        <v>78</v>
+      </c>
+      <c r="I26">
+        <v>23</v>
+      </c>
+      <c r="J26">
+        <v>20</v>
+      </c>
+      <c r="K26">
+        <v>9</v>
+      </c>
+      <c r="L26">
+        <v>18.2</v>
+      </c>
+      <c r="M26">
+        <v>10</v>
+      </c>
+      <c r="N26">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="O26">
+        <v>11.7</v>
+      </c>
+      <c r="P26" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>24</v>
+      </c>
+      <c r="B27">
+        <v>20</v>
+      </c>
+      <c r="C27">
+        <v>10</v>
+      </c>
+      <c r="D27">
+        <v>18.2</v>
+      </c>
+      <c r="E27">
+        <v>10</v>
+      </c>
+      <c r="F27" t="s">
+        <v>79</v>
+      </c>
+      <c r="I27">
+        <v>24</v>
+      </c>
+      <c r="J27">
+        <v>20</v>
+      </c>
+      <c r="K27">
+        <v>10</v>
+      </c>
+      <c r="L27">
+        <v>18.2</v>
+      </c>
+      <c r="M27">
+        <v>10</v>
+      </c>
+      <c r="N27">
+        <v>13.7</v>
+      </c>
+      <c r="O27">
+        <v>7.8</v>
+      </c>
+      <c r="P27" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="28" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>25</v>
+      </c>
+      <c r="B28">
+        <v>20</v>
+      </c>
+      <c r="C28">
+        <v>11</v>
+      </c>
+      <c r="D28">
+        <v>18.2</v>
+      </c>
+      <c r="E28">
+        <v>10</v>
+      </c>
+      <c r="F28" t="s">
+        <v>80</v>
+      </c>
+      <c r="I28">
+        <v>25</v>
+      </c>
+      <c r="J28">
+        <v>20</v>
+      </c>
+      <c r="K28">
+        <v>11</v>
+      </c>
+      <c r="L28">
+        <v>18.2</v>
+      </c>
+      <c r="M28">
+        <v>10</v>
+      </c>
+      <c r="N28">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="O28">
+        <v>17.2</v>
+      </c>
+      <c r="P28" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
